--- a/data/2025/13-cluj/54975-cluj-napoca/budget_file.xlsx
+++ b/data/2025/13-cluj/54975-cluj-napoca/budget_file.xlsx
@@ -9198,38 +9198,43 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
+      <c r="A183" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B183" s="4" t="inlineStr">
         <is>
           <t>51.02</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
+      <c r="C183" s="4" t="inlineStr">
         <is>
           <t>TITLUL I CHELTUIELI DE PERSONAL</t>
         </is>
       </c>
-      <c r="D183" t="n">
+      <c r="D183" s="4" t="n">
         <v>238</v>
       </c>
-      <c r="E183" t="n">
+      <c r="E183" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G183" s="3" t="n">
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="n">
         <v>118005000</v>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H183" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I183" s="4" t="inlineStr">
+        <is>
+          <t>10 total: parent 118.005.000,00 != sum(children) 115.475.000,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -9620,12 +9625,10 @@
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G194" s="5" t="n">
-        <v>2530000</v>
-      </c>
+      <c r="G194" s="5" t="n"/>
       <c r="H194" s="4" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
       <c r="I194" s="4" t="inlineStr">
@@ -19886,38 +19889,41 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="inlineStr">
+      <c r="A492" s="4" t="inlineStr">
         <is>
           <t>56.48</t>
         </is>
       </c>
-      <c r="B492" t="inlineStr">
+      <c r="B492" s="4" t="inlineStr">
         <is>
           <t>67.02</t>
         </is>
       </c>
-      <c r="C492" t="inlineStr">
+      <c r="C492" s="4" t="inlineStr">
         <is>
           <t>(FEDR), aferente cadrului financiar 2021-2027 (cod 56.48.01 la 56.48.03)</t>
         </is>
       </c>
-      <c r="D492" t="n">
+      <c r="D492" s="4" t="n">
         <v>550</v>
       </c>
-      <c r="E492" t="n">
+      <c r="E492" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="F492" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G492" s="3" t="n">
-        <v>50047000</v>
-      </c>
-      <c r="H492" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
+      <c r="F492" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G492" s="5" t="n"/>
+      <c r="H492" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I492" s="4" t="inlineStr">
+        <is>
+          <t>56.48 total: parent 0,00 != sum(children) 50.047.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -21477,38 +21483,43 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" t="inlineStr">
+      <c r="A541" s="4" t="inlineStr">
         <is>
           <t>20.05</t>
         </is>
       </c>
-      <c r="B541" t="inlineStr">
+      <c r="B541" s="4" t="inlineStr">
         <is>
           <t>68.02</t>
         </is>
       </c>
-      <c r="C541" t="inlineStr">
+      <c r="C541" s="4" t="inlineStr">
         <is>
           <t>Bunuri de natura obiectelor de inventar</t>
         </is>
       </c>
-      <c r="D541" t="n">
+      <c r="D541" s="4" t="n">
         <v>602</v>
       </c>
-      <c r="E541" t="n">
+      <c r="E541" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F541" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G541" s="3" t="n">
+      <c r="F541" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G541" s="5" t="n">
         <v>415000</v>
       </c>
-      <c r="H541" t="inlineStr">
-        <is>
-          <t>ocr</t>
+      <c r="H541" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I541" s="4" t="inlineStr">
+        <is>
+          <t>20.05 total: parent 415.000,00 != sum(children) 931.000,00 (3 children)</t>
         </is>
       </c>
     </row>
@@ -21613,11 +21624,11 @@
         </is>
       </c>
       <c r="G545" s="3" t="n">
-        <v>2000</v>
+        <v>385000</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -21649,11 +21660,11 @@
         </is>
       </c>
       <c r="G546" s="3" t="n">
-        <v>385000</v>
+        <v>518000</v>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -25472,38 +25483,43 @@
       </c>
     </row>
     <row r="661">
-      <c r="A661" t="inlineStr">
+      <c r="A661" s="4" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B661" s="4" t="inlineStr">
         <is>
           <t>74.02</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C661" s="4" t="inlineStr">
         <is>
           <t>TITLUL IV SUBVENTII</t>
         </is>
       </c>
-      <c r="D661" t="n">
+      <c r="D661" s="4" t="n">
         <v>722</v>
       </c>
-      <c r="E661" t="n">
+      <c r="E661" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F661" t="inlineStr">
-        <is>
-          <t>expense_economic</t>
-        </is>
-      </c>
-      <c r="G661" s="3" t="n">
-        <v>73000000</v>
-      </c>
-      <c r="H661" t="inlineStr">
-        <is>
-          <t>llm:gemini-3.6-flash</t>
+      <c r="F661" s="4" t="inlineStr">
+        <is>
+          <t>expense_economic</t>
+        </is>
+      </c>
+      <c r="G661" s="5" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="H661" s="4" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="I661" s="4" t="inlineStr">
+        <is>
+          <t>40 total: parent 48.000.000,00 != sum(children) 25.000.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -25534,12 +25550,10 @@
           <t>expense_economic</t>
         </is>
       </c>
-      <c r="G662" s="3" t="n">
-        <v>48000000</v>
-      </c>
+      <c r="G662" s="3" t="n"/>
       <c r="H662" t="inlineStr">
         <is>
-          <t>llm:gemini-3.6-flash</t>
+          <t>ocr</t>
         </is>
       </c>
     </row>
@@ -54276,7 +54290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -54322,12 +54336,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -54335,24 +54349,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>03.00.01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 11.02 total: still inconsistent — UNRESOLVED</t>
+          <t>code 03.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -54361,41 +54370,36 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.02</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>11.02.01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 30.02 total: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -54405,117 +54409,102 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 42.02 total: still inconsistent — UNRESOLVED</t>
+          <t>11.02 total: parent 278.780.000,00 != sum(children) 337.735.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>18.00.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 40 total: still inconsistent — UNRESOLVED</t>
+          <t>code 18.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>30.02.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 10 total: sum now consistent — applied</t>
+          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20.24</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>30.00.02</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 20.24 total: still inconsistent — UNRESOLVED</t>
+          <t>code 30.00.02 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -54525,87 +54514,77 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 20 total: still inconsistent — UNRESOLVED</t>
+          <t>30.02 total: parent 48.079.000,00 != sum(children) 73.066.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>56.48</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>33.00.01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 56.48 total: sum now consistent — applied</t>
+          <t>code 33.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20.05</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 20.05 total: sum now consistent — applied</t>
+          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -54615,27 +54594,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LLM re-read 3 rows for 40 total: sum now consistent — applied</t>
+          <t>42.02 total: parent 2.063.297.000,00 != sum(children) 2.079.403.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -54645,28 +54624,23 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 11.02 total: still inconsistent — UNRESOLVED</t>
+          <t>40 total: parent 104.111.000,00 != sum(children) 48.000.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>30.02</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -54675,14 +54649,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 30.02 total: still inconsistent — UNRESOLVED</t>
+          <t>unparseable cell '56.111.000 4.000.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -54691,28 +54665,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>50.04</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 10 total: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Fond de rezerva bugetara la dispozitia a'</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V6_repair</t>
+          <t>V2_name</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -54721,41 +54690,36 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10.01</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>55.01.84</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LLM re-read 5 rows for 10.01 total: still inconsistent — UNRESOLVED</t>
+          <t>name mismatch vs nomenclator (37%): 'Ssuan a er nu s z ate' vs 'Sume reprezentând stimulentul pentru cas'</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -54765,28 +54729,23 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 20 total: still inconsistent — UNRESOLVED</t>
+          <t>10 total: parent 118.005.000,00 != sum(children) 115.475.000,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -54795,28 +54754,23 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 20 total: still inconsistent — UNRESOLVED</t>
+          <t>unparseable cell '2.530.000 2.530.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>20.01</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -54825,27 +54779,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LLM re-read 6 rows for 20.01 total: still inconsistent — UNRESOLVED</t>
+          <t>unparseable cell '8.400.000 8.137.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -54855,27 +54809,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LLM re-read 4 rows for 58 total: still inconsistent — UNRESOLVED</t>
+          <t>20.24 total: parent 0,00 != sum(children) 500.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -54885,244 +54839,304 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LLM re-read 2 rows for 71.01 total: still inconsistent — UNRESOLVED</t>
+          <t>61.02 total: parent 67.596.000,00 != sum(children) 16.903.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p4: 0 cells recovered</t>
+          <t>unparseable cell '16.903.000 758.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p6: 0 cells recovered</t>
+          <t>20 total: parent 142.600.000,00 != sum(children) 129.628.000,00 (5 children)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p8: 0 cells recovered</t>
+          <t>unparseable cell '220.000 195.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p13: 0 cells recovered</t>
+          <t>unparseable cell '95.041.000 46.486.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p14: 0 cells recovered</t>
+          <t>67.02 total: parent 251.259.000,00 != sum(children) 66.629.000,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p21: 0 cells recovered</t>
+          <t>unparseable cell '50.047.000 50.047.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23</v>
+        <v>13</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>56.48</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p23: 0 cells recovered</t>
+          <t>56.48 total: parent 0,00 != sum(children) 50.047.000,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>13</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p24: 0 cells recovered</t>
+          <t>unparseable cell '21.000.000 21.000.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>V6_repair</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>info</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>29</v>
+        <v>14</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>unparseable-cell pass p29: 0 cells recovered</t>
+          <t>unparseable cell '3.965.000 132.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>03.00.01</t>
+          <t>20.01.02</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>code 03.00.01 (revenue) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (32%): 'Furnituri de birou' vs 'Materiale pentru curatenie'</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>11.02.01</t>
+        <v>14</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
+          <t>unparseable cell '301.000 700.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -55131,12 +55145,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>11.02</t>
-        </is>
+        <v>14</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -55145,64 +55154,69 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>11.02 total: parent 278.780.000,00 != sum(children) 337.735.000,00 (1 children)</t>
+          <t>unparseable cell '200.000 200.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>18.00.01</t>
+          <t>20.04.04</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>code 18.00.01 (revenue) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (39%): 'Materiale sanitare' vs 'Dezinfectanti'</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>30.02.01</t>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
+          <t>20.05 total: parent 415.000,00 != sum(children) 931.000,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -55211,16 +55225,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>30.00.02</t>
+        <v>14</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>code 30.00.02 (revenue) not in nomenclator</t>
+          <t>unparseable cell '80.000 166.000' in column total</t>
         </is>
       </c>
     </row>
@@ -55236,11 +55250,11 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -55250,14 +55264,14 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>30.02 total: parent 48.079.000,00 != sum(children) 73.066.000,00 (1 children)</t>
+          <t>70.02 total: parent 258.881.000,00 != sum(children) 68.743.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -55266,16 +55280,21 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>33.00.01</t>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>code 33.00.01 (revenue) not in nomenclator</t>
+          <t>74.02 total: parent 177.368.000,00 != sum(children) 3.094.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -55291,23 +55310,23 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>42.02.01</t>
+          <t>55.01.84</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
+          <t>name mismatch vs nomenclator (31%): 'Ssunn a ra und  a ate' vs 'Sume reprezentând stimulentul pentru cas'</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -55316,12 +55335,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>42.02</t>
-        </is>
+        <v>17</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -55330,7 +55344,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>42.02 total: parent 2.063.297.000,00 != sum(children) 2.079.403.000,00 (1 children)</t>
+          <t>unparseable cell '2.167.461.000 103.071.000' in column total</t>
         </is>
       </c>
     </row>
@@ -55346,7 +55360,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -55360,7 +55374,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>40 total: parent 104.111.000,00 != sum(children) 48.000.000,00 (1 children)</t>
+          <t>40 total: parent 48.000.000,00 != sum(children) 25.000.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -55376,7 +55390,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -55385,89 +55399,94 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>unparseable cell '56.111.000 4.000.000' in column total</t>
+          <t>unparseable cell '6.026.000 6.026.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>50.04</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Fond de rezerva bugetara la dispozitia a'</t>
+          <t>84.02 total: parent 2.063.790.000,00 != sum(children) 153.519.000,00 (2 children)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V1_code</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>55.01.84</t>
+          <t>03.00.01</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (37%): 'Ssuan a er nu s z ate' vs 'Sume reprezentând stimulentul pentru cas'</t>
+          <t>code 03.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>total</t>
+        <v>19</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>11.02.01</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>unparseable cell '2.530.000 2.530.000' in column total</t>
+          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -55476,7 +55495,12 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>8</v>
+        <v>19</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>11.02</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -55485,14 +55509,14 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>unparseable cell '8.400.000 8.137.000' in column total</t>
+          <t>11.02 total: parent 278.780.000,00 != sum(children) 337.735.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -55501,58 +55525,48 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20.24</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>18.00.01</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20.24 total: parent 0,00 != sum(children) 500.000,00 (1 children)</t>
+          <t>code 18.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>61.02</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>30.02.01</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.02 total: parent 67.596.000,00 != sum(children) 16.903.000,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -55561,16 +55575,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>total</t>
+        <v>19</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>30.00.02</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>unparseable cell '16.903.000 758.000' in column total</t>
+          <t>code 30.00.02 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
@@ -55586,11 +55600,11 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -55600,14 +55614,14 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20 total: parent 142.600.000,00 != sum(children) 129.628.000,00 (5 children)</t>
+          <t>30.02 total: parent 48.079.000,00 != sum(children) -65.145.400,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -55616,48 +55630,48 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>total</t>
+        <v>20</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>33.00.01</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>unparseable cell '220.000 195.000' in column total</t>
+          <t>code 33.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>11</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>total</t>
+        <v>20</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>unparseable cell '95.041.000 46.486.000' in column total</t>
+          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -55666,12 +55680,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>13</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
+        <v>21</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -55680,39 +55689,39 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>67.02 total: parent 251.259.000,00 != sum(children) 66.629.000,00 (2 children)</t>
+          <t>unparseable cell '47.260.000 104.111.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>13</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>total</t>
+        <v>22</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>55.01.84</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>unparseable cell '50.047.000 50.047.000' in column total</t>
+          <t>name mismatch vs nomenclator (30%): 'Ssuan a a ua   ate' vs 'Sume reprezentând stimulentul pentru cas'</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -55721,7 +55730,12 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -55730,14 +55744,14 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>unparseable cell '21.000.000 21.000.000' in column total</t>
+          <t>10 total: parent 8.400.000,00 != sum(children) 8.137.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -55746,7 +55760,12 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>14</v>
+        <v>23</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>10.01</t>
+        </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -55755,39 +55774,39 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>unparseable cell '3.965.000 132.000' in column total</t>
+          <t>10.01 total: parent 8.137.000,00 != sum(children) 7.955.000,00 (4 children)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>14</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>20.01.02</t>
+        <v>23</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'Furnituri de birou' vs 'Materiale pentru curatenie'</t>
+          <t>unparseable cell '182.000 79.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -55796,7 +55815,12 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -55805,7 +55829,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>unparseable cell '301.000 700.000' in column total</t>
+          <t>20 total: parent 7.513.000,00 != sum(children) 4.921.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -55821,7 +55845,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -55830,39 +55854,44 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>unparseable cell '200.000 200.000' in column total</t>
+          <t>unparseable cell '300.000 10.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V4_hierarchy</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20.04.04</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (39%): 'Materiale sanitare' vs 'Dezinfectanti'</t>
+          <t>20 total: parent 142.600.000,00 != sum(children) 84.324.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -55871,7 +55900,12 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>14</v>
+        <v>25</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>20.01</t>
+        </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -55880,14 +55914,14 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>unparseable cell '80.000 166.000' in column total</t>
+          <t>20.01 total: parent 84.324.000,00 != sum(children) 46.340.000,00 (5 children)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -55896,12 +55930,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>15</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>70.02</t>
-        </is>
+        <v>25</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -55910,69 +55939,64 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>70.02 total: parent 258.881.000,00 != sum(children) 68.743.000,00 (1 children)</t>
+          <t>unparseable cell '625.000 86.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>20.01.08</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>74.02 total: parent 177.368.000,00 != sum(children) 3.094.000,00 (1 children)</t>
+          <t>name mismatch vs nomenclator (0%): '' vs 'Posta, telecomunicatii, radio, tv, inter'</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>17</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>55.01.84</t>
+        <v>26</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (31%): 'Ssunn a ra und  a ate' vs 'Sume reprezentând stimulentul pentru cas'</t>
+          <t>unparseable cell '2.185.000 2.185.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -55981,7 +56005,12 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>17</v>
+        <v>27</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>67.02</t>
+        </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -55990,7 +56019,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>unparseable cell '2.167.461.000 103.071.000' in column total</t>
+          <t>67.02 total: parent 155.583.000,00 != sum(children) 21.000.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -56006,7 +56035,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -56015,44 +56044,39 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>unparseable cell '6.026.000 6.026.000' in column total</t>
+          <t>unparseable cell '12.700.000 80.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>55.01.84</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>84.02 total: parent 2.063.790.000,00 != sum(children) 153.519.000,00 (2 children)</t>
+          <t>name mismatch vs nomenclator (37%): 'Ssutn na uear nu   ate' vs 'Sume reprezentând stimulentul pentru cas'</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -56061,16 +56085,21 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>03.00.01</t>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>code 03.00.01 (revenue) not in nomenclator</t>
+          <t>84.02 total: parent 172.350.000,00 != sum(children) 17.979.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -56086,23 +56115,23 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>11.02.01</t>
+          <t>30.02.01</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (33%): 'A4. IMPOZITE SI TAXE PE BUNURI SI SERVIC' vs 'Sume defalcate din taxa pe valoarea adau'</t>
+          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
+          <t>V1_code</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -56111,53 +56140,48 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>11.02</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>33.00.01</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>11.02 total: parent 278.780.000,00 != sum(children) 337.735.000,00 (1 children)</t>
+          <t>code 33.00.01 (revenue) not in nomenclator</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V2_name</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>18.00.01</t>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>code 18.00.01 (revenue) not in nomenclator</t>
+          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>V2_name</t>
+          <t>V7_hygiene</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -56166,78 +56190,73 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>30.02.01</t>
+          <t>42.02.01</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>30.00.02</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>code 30.00.02 (revenue) not in nomenclator</t>
+          <t>duplicate of p2 with different values</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>warning</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>30.02</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>total</t>
+          <t>01</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>30.02 total: parent 48.079.000,00 != sum(children) -65.145.400,00 (1 children)</t>
+          <t>duplicate of p3 with different values</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>V1_code</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -56246,48 +56265,53 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>33.00.01</t>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>code 33.00.01 (revenue) not in nomenclator</t>
+          <t>58 total: parent 28.809.000,00 != sum(children) 4.764.000,00 (3 children)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>20</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>42.02.01</t>
+        <v>33</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
+          <t>unparseable cell '279.000 24.045.000' in column total</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -56296,7 +56320,12 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>21</v>
+        <v>34</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>71.01</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -56305,32 +56334,32 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>unparseable cell '47.260.000 104.111.000' in column total</t>
+          <t>71.01 total: parent 226.183.000,00 != sum(children) 205.746.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>warning</t>
+          <t>V7_hygiene</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>22</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>55.01.84</t>
+        <v>34</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>total</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>name mismatch vs nomenclator (30%): 'Ssuan a a ua   ate' vs 'Sume reprezentând stimulentul pentru cas'</t>
+          <t>unparseable cell '20.437.000 236.404.004' in column total</t>
         </is>
       </c>
     </row>
@@ -56346,11 +56375,11 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -56360,7 +56389,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>10 total: parent 8.400.000,00 != sum(children) 8.137.000,00 (1 children)</t>
+          <t>65.02 total: parent 489.650.026,00 != sum(children) 226.076.026,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -56376,11 +56405,11 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -56390,14 +56419,14 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>10.01 total: parent 8.137.000,00 != sum(children) 7.955.000,00 (4 children)</t>
+          <t>67.02 total: parent 95.676.000,00 != sum(children) 45.629.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -56406,7 +56435,12 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>23</v>
+        <v>36</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>68.02</t>
+        </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -56415,7 +56449,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>unparseable cell '182.000 79.000' in column total</t>
+          <t>68.02 total: parent 49.864.000,00 != sum(children) 45.112.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -56431,11 +56465,11 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -56445,14 +56479,14 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>20 total: parent 7.513.000,00 != sum(children) 4.921.000,00 (1 children)</t>
+          <t>70.02 total: parent 104.283.000,00 != sum(children) 68.743.000,00 (1 children)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>V7_hygiene</t>
+          <t>V4_hierarchy</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -56461,7 +56495,12 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>24</v>
+        <v>37</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>74.02</t>
+        </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -56470,7 +56509,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>unparseable cell '300.000 10.000' in column total</t>
+          <t>74.02 total: parent 73.067.000,00 != sum(children) 3.094.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -56486,11 +56525,11 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -56500,7 +56539,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>20 total: parent 142.600.000,00 != sum(children) 84.324.000,00 (1 children)</t>
+          <t>81.02 total: parent 30.071.000,00 != sum(children) 6.026.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -56516,11 +56555,11 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -56529,661 +56568,6 @@
         </is>
       </c>
       <c r="F84" t="inlineStr">
-        <is>
-          <t>20.01 total: parent 84.324.000,00 != sum(children) 46.340.000,00 (5 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>25</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>unparseable cell '625.000 86.000' in column total</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>25</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>20.01.08</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (0%): '' vs 'Posta, telecomunicatii, radio, tv, inter'</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>26</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>unparseable cell '2.185.000 2.185.000' in column total</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>27</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>67.02 total: parent 155.583.000,00 != sum(children) 21.000.000,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>29</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>unparseable cell '12.700.000 80.000' in column total</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>31</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>55.01.84</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (37%): 'Ssutn na uear nu   ate' vs 'Sume reprezentând stimulentul pentru cas'</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>31</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>84.02 total: parent 172.350.000,00 != sum(children) 17.979.000,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>32</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>30.02.01</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (32%): 'C. VENITURI NEFISCALE' vs 'Varsaminte din profitul net al regiilor '</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>V1_code</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>32</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>33.00.01</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>code 33.00.01 (revenue) not in nomenclator</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>V2_name</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>32</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>42.02.01</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>name mismatch vs nomenclator (18%): 'IV. SUBVENTII' vs 'Programul Termoficare'</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>32</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>42.02.01</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>duplicate of p2 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>32</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>42.02</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>duplicate of p2 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>33</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>duplicate of p3 with different values</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>33</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>58 total: parent 28.809.000,00 != sum(children) 4.764.000,00 (3 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>33</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>unparseable cell '279.000 24.045.000' in column total</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>34</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>71.01</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>71.01 total: parent 226.183.000,00 != sum(children) 205.746.000,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>V7_hygiene</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>34</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>unparseable cell '20.437.000 236.404.004' in column total</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>35</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>65.02 total: parent 489.650.026,00 != sum(children) 226.076.026,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>36</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>67.02</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>67.02 total: parent 95.676.000,00 != sum(children) 45.629.000,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>36</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>68.02</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>68.02 total: parent 49.864.000,00 != sum(children) 45.112.000,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>37</v>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>70.02 total: parent 104.283.000,00 != sum(children) 68.743.000,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>37</v>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>74.02</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>74.02 total: parent 73.067.000,00 != sum(children) 3.094.000,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>37</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>81.02</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>81.02 total: parent 30.071.000,00 != sum(children) 6.026.000,00 (1 children)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>V4_hierarchy</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>38</v>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>84.02</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
         <is>
           <t>84.02 total: parent 1.891.440.000,00 != sum(children) 135.540.000,00 (1 children)</t>
         </is>
@@ -57200,7 +56584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -57222,7 +56606,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Documente</t>
+          <t>Schema calitate</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -57232,72 +56616,230 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Linii de date</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1294</v>
+          <t>Metrica de calitate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>observed_strict_line_rate</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1234</v>
+          <t>Recall masurat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>% curat</t>
+          <t>Documente</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95.40000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii de date</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>Linii strict verificate</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Modele LLM folosite</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>gemini-3.6-flash</t>
-        </is>
+          <t>% linii strict verificate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>— BUGETUL LOCAL PE ANUL — Anexa 2</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+          <t>Celule numerice</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>% celule numerice strict verificate</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pagini asteptate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pagini procesate</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Linii fara probleme</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>% curat</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>95.09999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Erori</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Avertismente</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Bundle conversie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>a919498cd777e3700102c702</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>7071747e95b9f326fc8d44baaee1d143d9fc89dc7b3beecefec1569cf7c3beba</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>— BUGETUL LOCAL PE ANUL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>local, pag. 1-38, 1642 linii</t>
         </is>
